--- a/samples/checked/monthly/月次クレーム集計2602.xlsx
+++ b/samples/checked/monthly/月次クレーム集計2602.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月次集計" sheetId="1" r:id="Rf1e2bf2a4b6d4f99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="期待結果" sheetId="2" r:id="R07272c8fec35437d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="マスタ" sheetId="3" r:id="R1a945898e7f243e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="異常系" sheetId="4" r:id="Rf6113f43da574f3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月次集計" sheetId="1" r:id="R62530cd96bf545a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="期待結果" sheetId="2" r:id="R3db6a4bf0ad94abf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="マスタ" sheetId="3" r:id="R1431c0d27d834fd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="異常系" sheetId="4" r:id="R4a922025fbb8478e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -302,11 +302,11 @@
   <x:cols>
     <x:col min="1" max="1" width="16.8799991607666" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="10.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="5.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="3.880000114440918" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="8.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="23.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="8.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="12.5" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="8.880000114440918" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="1.5" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="1.5" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="1.5" hidden="0" customWidth="1"/>
@@ -339,7 +339,7 @@
     <x:col min="37" max="37" width="2.5" hidden="0" customWidth="1"/>
     <x:col min="38" max="38" width="2.5" hidden="0" customWidth="1"/>
     <x:col min="39" max="39" width="5.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="40" max="40" width="24.75" hidden="0" customWidth="1"/>
+    <x:col min="40" max="40" width="27.1299991607666" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -516,19 +516,19 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="C4" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="E4" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="F4" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="G4" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="H4" s="5" t="str"/>
       <x:c r="I4" s="5" t="str"/>
@@ -575,19 +575,19 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="E5" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="F5" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="G5" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="H5" s="5" t="str"/>
       <x:c r="I5" s="5" t="str"/>
@@ -634,19 +634,19 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="E6" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="F6" s="5" t="str">
         <x:v>REP</x:v>
       </x:c>
       <x:c r="G6" s="5" t="str">
-        <x:v>Repair Desk</x:v>
+        <x:v>修理受付</x:v>
       </x:c>
       <x:c r="H6" s="5" t="str"/>
       <x:c r="I6" s="5" t="str"/>
@@ -693,19 +693,19 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="E7" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="F7" s="5" t="str">
         <x:v>BIL</x:v>
       </x:c>
       <x:c r="G7" s="5" t="str">
-        <x:v>Billing Desk</x:v>
+        <x:v>請求確認</x:v>
       </x:c>
       <x:c r="H7" s="5" t="str"/>
       <x:c r="I7" s="5" t="str"/>
@@ -752,11 +752,11 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="C8" s="12" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D8" s="12" t="str"/>
       <x:c r="E8" s="12" t="str">
-        <x:v>Aster Central subtotal</x:v>
+        <x:v>あかね中央支店 小計</x:v>
       </x:c>
       <x:c r="F8" s="12" t="str"/>
       <x:c r="G8" s="12" t="str"/>
@@ -889,7 +889,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AN8" s="12" t="str">
-        <x:v>subtotal row; not an input key</x:v>
+        <x:v>小計行。入力キーではありません。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -897,22 +897,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
         <x:v>BR02</x:v>
       </x:c>
       <x:c r="E9" s="5" t="str">
-        <x:v>Beryl Annex</x:v>
+        <x:v>ひすい北支店</x:v>
       </x:c>
       <x:c r="F9" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="G9" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="H9" s="5" t="str"/>
       <x:c r="I9" s="5" t="str"/>
@@ -956,22 +956,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B10" s="5" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
       <x:c r="C10" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D10" s="5" t="str">
         <x:v>BR02</x:v>
       </x:c>
       <x:c r="E10" s="5" t="str">
-        <x:v>Beryl Annex</x:v>
+        <x:v>ひすい北支店</x:v>
       </x:c>
       <x:c r="F10" s="5" t="str">
         <x:v>DEL</x:v>
       </x:c>
       <x:c r="G10" s="5" t="str">
-        <x:v>Delivery Desk</x:v>
+        <x:v>配送調整</x:v>
       </x:c>
       <x:c r="H10" s="5" t="str"/>
       <x:c r="I10" s="5" t="str"/>
@@ -1015,22 +1015,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B11" s="5" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
       <x:c r="C11" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D11" s="5" t="str">
         <x:v>BR02</x:v>
       </x:c>
       <x:c r="E11" s="5" t="str">
-        <x:v>Beryl Annex</x:v>
+        <x:v>ひすい北支店</x:v>
       </x:c>
       <x:c r="F11" s="5" t="str">
         <x:v>APP</x:v>
       </x:c>
       <x:c r="G11" s="5" t="str">
-        <x:v>App Support</x:v>
+        <x:v>アプリ支援</x:v>
       </x:c>
       <x:c r="H11" s="5" t="str"/>
       <x:c r="I11" s="5" t="str"/>
@@ -1074,14 +1074,14 @@
         <x:v>SUBTOTAL</x:v>
       </x:c>
       <x:c r="B12" s="12" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
       <x:c r="C12" s="12" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D12" s="12" t="str"/>
       <x:c r="E12" s="12" t="str">
-        <x:v>North small-branch subtotal</x:v>
+        <x:v>北部小支店 小計</x:v>
       </x:c>
       <x:c r="F12" s="12" t="str"/>
       <x:c r="G12" s="12" t="str"/>
@@ -1214,7 +1214,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AN12" s="12" t="str">
-        <x:v>subtotal row; not an input key</x:v>
+        <x:v>小計行。入力キーではありません。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1222,22 +1222,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B13" s="5" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
       <x:c r="C13" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D13" s="5" t="str">
         <x:v>BR03</x:v>
       </x:c>
       <x:c r="E13" s="5" t="str">
-        <x:v>Cobalt East</x:v>
+        <x:v>こはく東支店</x:v>
       </x:c>
       <x:c r="F13" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="G13" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="H13" s="5" t="str"/>
       <x:c r="I13" s="5" t="str"/>
@@ -1281,22 +1281,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B14" s="5" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
       <x:c r="C14" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D14" s="5" t="str">
         <x:v>BR03</x:v>
       </x:c>
       <x:c r="E14" s="5" t="str">
-        <x:v>Cobalt East</x:v>
+        <x:v>こはく東支店</x:v>
       </x:c>
       <x:c r="F14" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="G14" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="H14" s="5" t="str"/>
       <x:c r="I14" s="5" t="str"/>
@@ -1340,22 +1340,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B15" s="5" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
       <x:c r="C15" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D15" s="5" t="str">
         <x:v>BR03</x:v>
       </x:c>
       <x:c r="E15" s="5" t="str">
-        <x:v>Cobalt East</x:v>
+        <x:v>こはく東支店</x:v>
       </x:c>
       <x:c r="F15" s="5" t="str">
         <x:v>CON</x:v>
       </x:c>
       <x:c r="G15" s="5" t="str">
-        <x:v>Contract Desk</x:v>
+        <x:v>契約確認</x:v>
       </x:c>
       <x:c r="H15" s="5" t="str"/>
       <x:c r="I15" s="5" t="str"/>
@@ -1399,14 +1399,14 @@
         <x:v>SUBTOTAL</x:v>
       </x:c>
       <x:c r="B16" s="12" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
       <x:c r="C16" s="12" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D16" s="12" t="str"/>
       <x:c r="E16" s="12" t="str">
-        <x:v>East small-branch subtotal</x:v>
+        <x:v>東部小支店 小計</x:v>
       </x:c>
       <x:c r="F16" s="12" t="str"/>
       <x:c r="G16" s="12" t="str"/>
@@ -1539,7 +1539,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AN16" s="12" t="str">
-        <x:v>subtotal row; not an input key</x:v>
+        <x:v>小計行。入力キーではありません。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1550,19 +1550,19 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C17" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D17" s="5" t="str">
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="E17" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="F17" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="G17" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="H17" s="5" t="str"/>
       <x:c r="I17" s="5" t="str"/>
@@ -1609,19 +1609,19 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C18" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D18" s="5" t="str">
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="E18" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="F18" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="G18" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="H18" s="5" t="str"/>
       <x:c r="I18" s="5" t="str"/>
@@ -1668,19 +1668,19 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C19" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D19" s="5" t="str">
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="E19" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="F19" s="5" t="str">
         <x:v>REP</x:v>
       </x:c>
       <x:c r="G19" s="5" t="str">
-        <x:v>Repair Desk</x:v>
+        <x:v>修理受付</x:v>
       </x:c>
       <x:c r="H19" s="5" t="str"/>
       <x:c r="I19" s="5" t="str"/>
@@ -1727,19 +1727,19 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C20" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D20" s="5" t="str">
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="E20" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="F20" s="5" t="str">
         <x:v>DEL</x:v>
       </x:c>
       <x:c r="G20" s="5" t="str">
-        <x:v>Delivery Desk</x:v>
+        <x:v>配送調整</x:v>
       </x:c>
       <x:c r="H20" s="5" t="str"/>
       <x:c r="I20" s="5" t="str"/>
@@ -1786,19 +1786,19 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C21" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D21" s="5" t="str">
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="E21" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="F21" s="5" t="str">
         <x:v>BIL</x:v>
       </x:c>
       <x:c r="G21" s="5" t="str">
-        <x:v>Billing Desk</x:v>
+        <x:v>請求確認</x:v>
       </x:c>
       <x:c r="H21" s="5" t="str"/>
       <x:c r="I21" s="5" t="str"/>
@@ -1845,11 +1845,11 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C22" s="12" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D22" s="12" t="str"/>
       <x:c r="E22" s="12" t="str">
-        <x:v>Dahlia Hub subtotal</x:v>
+        <x:v>だりあ東支店 小計</x:v>
       </x:c>
       <x:c r="F22" s="12" t="str"/>
       <x:c r="G22" s="12" t="str"/>
@@ -1982,7 +1982,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AN22" s="12" t="str">
-        <x:v>subtotal row; not an input key</x:v>
+        <x:v>小計行。入力キーではありません。</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1990,22 +1990,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B23" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C23" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D23" s="5" t="str">
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="E23" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="F23" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="G23" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="H23" s="5" t="str"/>
       <x:c r="I23" s="5" t="str"/>
@@ -2049,22 +2049,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B24" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C24" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D24" s="5" t="str">
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="E24" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="F24" s="5" t="str">
         <x:v>APP</x:v>
       </x:c>
       <x:c r="G24" s="5" t="str">
-        <x:v>App Support</x:v>
+        <x:v>アプリ支援</x:v>
       </x:c>
       <x:c r="H24" s="5" t="str"/>
       <x:c r="I24" s="5" t="str"/>
@@ -2108,22 +2108,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B25" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C25" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D25" s="5" t="str">
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="E25" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="F25" s="5" t="str">
         <x:v>CON</x:v>
       </x:c>
       <x:c r="G25" s="5" t="str">
-        <x:v>Contract Desk</x:v>
+        <x:v>契約確認</x:v>
       </x:c>
       <x:c r="H25" s="5" t="str"/>
       <x:c r="I25" s="5" t="str"/>
@@ -2167,22 +2167,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B26" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C26" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D26" s="5" t="str">
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="E26" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="F26" s="5" t="str">
         <x:v>OTH</x:v>
       </x:c>
       <x:c r="G26" s="5" t="str">
-        <x:v>Other Desk</x:v>
+        <x:v>その他対応</x:v>
       </x:c>
       <x:c r="H26" s="5" t="str"/>
       <x:c r="I26" s="5" t="str"/>
@@ -2226,14 +2226,14 @@
         <x:v>SUBTOTAL</x:v>
       </x:c>
       <x:c r="B27" s="12" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C27" s="12" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D27" s="12" t="str"/>
       <x:c r="E27" s="12" t="str">
-        <x:v>South small-branch subtotal</x:v>
+        <x:v>南部小支店 小計</x:v>
       </x:c>
       <x:c r="F27" s="12" t="str"/>
       <x:c r="G27" s="12" t="str"/>
@@ -2366,7 +2366,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AN27" s="12" t="str">
-        <x:v>subtotal row; not an input key</x:v>
+        <x:v>小計行。入力キーではありません。</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -2374,22 +2374,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B28" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C28" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D28" s="5" t="str">
         <x:v>BR06</x:v>
       </x:c>
       <x:c r="E28" s="5" t="str">
-        <x:v>Fennel South</x:v>
+        <x:v>ふじ南支店</x:v>
       </x:c>
       <x:c r="F28" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="G28" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="H28" s="5" t="str"/>
       <x:c r="I28" s="5" t="str"/>
@@ -2433,22 +2433,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B29" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C29" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D29" s="5" t="str">
         <x:v>BR06</x:v>
       </x:c>
       <x:c r="E29" s="5" t="str">
-        <x:v>Fennel South</x:v>
+        <x:v>ふじ南支店</x:v>
       </x:c>
       <x:c r="F29" s="5" t="str">
         <x:v>DEL</x:v>
       </x:c>
       <x:c r="G29" s="5" t="str">
-        <x:v>Delivery Desk</x:v>
+        <x:v>配送調整</x:v>
       </x:c>
       <x:c r="H29" s="5" t="str"/>
       <x:c r="I29" s="5" t="str"/>
@@ -2492,22 +2492,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B30" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C30" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D30" s="5" t="str">
         <x:v>BR06</x:v>
       </x:c>
       <x:c r="E30" s="5" t="str">
-        <x:v>Fennel South</x:v>
+        <x:v>ふじ南支店</x:v>
       </x:c>
       <x:c r="F30" s="5" t="str">
         <x:v>OTH</x:v>
       </x:c>
       <x:c r="G30" s="5" t="str">
-        <x:v>Other Desk</x:v>
+        <x:v>その他対応</x:v>
       </x:c>
       <x:c r="H30" s="5" t="str"/>
       <x:c r="I30" s="5" t="str"/>
@@ -2557,11 +2557,11 @@
   <x:cols>
     <x:col min="1" max="1" width="16.8799991607666" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="10.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="5.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="3.880000114440918" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="8.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="23.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="8.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="12.5" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="8.880000114440918" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="1.5" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="1.5" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="1.5" hidden="0" customWidth="1"/>
@@ -2594,7 +2594,7 @@
     <x:col min="37" max="37" width="2.5" hidden="0" customWidth="1"/>
     <x:col min="38" max="38" width="2.5" hidden="0" customWidth="1"/>
     <x:col min="39" max="39" width="5.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="40" max="40" width="24.75" hidden="0" customWidth="1"/>
+    <x:col min="40" max="40" width="27.1299991607666" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -2771,19 +2771,19 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="C4" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="E4" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="F4" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="G4" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="H4" s="5" t="n">
         <x:v>3</x:v>
@@ -2833,19 +2833,19 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="E5" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="F5" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="G5" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="H5" s="5" t="n">
         <x:v>1</x:v>
@@ -2893,19 +2893,19 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="E6" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="F6" s="5" t="str">
         <x:v>REP</x:v>
       </x:c>
       <x:c r="G6" s="5" t="str">
-        <x:v>Repair Desk</x:v>
+        <x:v>修理受付</x:v>
       </x:c>
       <x:c r="H6" s="5" t="str"/>
       <x:c r="I6" s="5" t="str"/>
@@ -2949,19 +2949,19 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="E7" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="F7" s="5" t="str">
         <x:v>BIL</x:v>
       </x:c>
       <x:c r="G7" s="5" t="str">
-        <x:v>Billing Desk</x:v>
+        <x:v>請求確認</x:v>
       </x:c>
       <x:c r="H7" s="5" t="str"/>
       <x:c r="I7" s="5" t="str"/>
@@ -3005,11 +3005,11 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="C8" s="12" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D8" s="12" t="str"/>
       <x:c r="E8" s="12" t="str">
-        <x:v>Aster Central subtotal</x:v>
+        <x:v>あかね中央支店 小計</x:v>
       </x:c>
       <x:c r="F8" s="12" t="str"/>
       <x:c r="G8" s="12" t="str"/>
@@ -3052,7 +3052,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AN8" s="12" t="str">
-        <x:v>subtotal row; not an input key</x:v>
+        <x:v>小計行。入力キーではありません。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3060,22 +3060,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
         <x:v>BR02</x:v>
       </x:c>
       <x:c r="E9" s="5" t="str">
-        <x:v>Beryl Annex</x:v>
+        <x:v>ひすい北支店</x:v>
       </x:c>
       <x:c r="F9" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="G9" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="H9" s="5" t="str"/>
       <x:c r="I9" s="5" t="str"/>
@@ -3116,22 +3116,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B10" s="5" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
       <x:c r="C10" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D10" s="5" t="str">
         <x:v>BR02</x:v>
       </x:c>
       <x:c r="E10" s="5" t="str">
-        <x:v>Beryl Annex</x:v>
+        <x:v>ひすい北支店</x:v>
       </x:c>
       <x:c r="F10" s="5" t="str">
         <x:v>DEL</x:v>
       </x:c>
       <x:c r="G10" s="5" t="str">
-        <x:v>Delivery Desk</x:v>
+        <x:v>配送調整</x:v>
       </x:c>
       <x:c r="H10" s="5" t="n">
         <x:v>2</x:v>
@@ -3176,22 +3176,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B11" s="5" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
       <x:c r="C11" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D11" s="5" t="str">
         <x:v>BR02</x:v>
       </x:c>
       <x:c r="E11" s="5" t="str">
-        <x:v>Beryl Annex</x:v>
+        <x:v>ひすい北支店</x:v>
       </x:c>
       <x:c r="F11" s="5" t="str">
         <x:v>APP</x:v>
       </x:c>
       <x:c r="G11" s="5" t="str">
-        <x:v>App Support</x:v>
+        <x:v>アプリ支援</x:v>
       </x:c>
       <x:c r="H11" s="5" t="str"/>
       <x:c r="I11" s="5" t="str"/>
@@ -3236,14 +3236,14 @@
         <x:v>SUBTOTAL</x:v>
       </x:c>
       <x:c r="B12" s="12" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
       <x:c r="C12" s="12" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D12" s="12" t="str"/>
       <x:c r="E12" s="12" t="str">
-        <x:v>North small-branch subtotal</x:v>
+        <x:v>北部小支店 小計</x:v>
       </x:c>
       <x:c r="F12" s="12" t="str"/>
       <x:c r="G12" s="12" t="str"/>
@@ -3286,7 +3286,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AN12" s="12" t="str">
-        <x:v>subtotal row; not an input key</x:v>
+        <x:v>小計行。入力キーではありません。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -3294,22 +3294,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B13" s="5" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
       <x:c r="C13" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D13" s="5" t="str">
         <x:v>BR03</x:v>
       </x:c>
       <x:c r="E13" s="5" t="str">
-        <x:v>Cobalt East</x:v>
+        <x:v>こはく東支店</x:v>
       </x:c>
       <x:c r="F13" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="G13" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="H13" s="5" t="str"/>
       <x:c r="I13" s="5" t="str"/>
@@ -3350,22 +3350,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B14" s="5" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
       <x:c r="C14" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D14" s="5" t="str">
         <x:v>BR03</x:v>
       </x:c>
       <x:c r="E14" s="5" t="str">
-        <x:v>Cobalt East</x:v>
+        <x:v>こはく東支店</x:v>
       </x:c>
       <x:c r="F14" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="G14" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="H14" s="5" t="str"/>
       <x:c r="I14" s="5" t="str"/>
@@ -3410,22 +3410,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B15" s="5" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
       <x:c r="C15" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D15" s="5" t="str">
         <x:v>BR03</x:v>
       </x:c>
       <x:c r="E15" s="5" t="str">
-        <x:v>Cobalt East</x:v>
+        <x:v>こはく東支店</x:v>
       </x:c>
       <x:c r="F15" s="5" t="str">
         <x:v>CON</x:v>
       </x:c>
       <x:c r="G15" s="5" t="str">
-        <x:v>Contract Desk</x:v>
+        <x:v>契約確認</x:v>
       </x:c>
       <x:c r="H15" s="5" t="str"/>
       <x:c r="I15" s="5" t="n">
@@ -3470,14 +3470,14 @@
         <x:v>SUBTOTAL</x:v>
       </x:c>
       <x:c r="B16" s="12" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
       <x:c r="C16" s="12" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D16" s="12" t="str"/>
       <x:c r="E16" s="12" t="str">
-        <x:v>East small-branch subtotal</x:v>
+        <x:v>東部小支店 小計</x:v>
       </x:c>
       <x:c r="F16" s="12" t="str"/>
       <x:c r="G16" s="12" t="str"/>
@@ -3520,7 +3520,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AN16" s="12" t="str">
-        <x:v>subtotal row; not an input key</x:v>
+        <x:v>小計行。入力キーではありません。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -3531,19 +3531,19 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C17" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D17" s="5" t="str">
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="E17" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="F17" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="G17" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="H17" s="5" t="str"/>
       <x:c r="I17" s="5" t="str"/>
@@ -3587,19 +3587,19 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C18" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D18" s="5" t="str">
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="E18" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="F18" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="G18" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="H18" s="5" t="str"/>
       <x:c r="I18" s="5" t="str"/>
@@ -3643,19 +3643,19 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C19" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D19" s="5" t="str">
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="E19" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="F19" s="5" t="str">
         <x:v>REP</x:v>
       </x:c>
       <x:c r="G19" s="5" t="str">
-        <x:v>Repair Desk</x:v>
+        <x:v>修理受付</x:v>
       </x:c>
       <x:c r="H19" s="5" t="n">
         <x:v>5</x:v>
@@ -3703,19 +3703,19 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C20" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D20" s="5" t="str">
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="E20" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="F20" s="5" t="str">
         <x:v>DEL</x:v>
       </x:c>
       <x:c r="G20" s="5" t="str">
-        <x:v>Delivery Desk</x:v>
+        <x:v>配送調整</x:v>
       </x:c>
       <x:c r="H20" s="5" t="str"/>
       <x:c r="I20" s="5" t="str"/>
@@ -3763,19 +3763,19 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C21" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D21" s="5" t="str">
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="E21" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="F21" s="5" t="str">
         <x:v>BIL</x:v>
       </x:c>
       <x:c r="G21" s="5" t="str">
-        <x:v>Billing Desk</x:v>
+        <x:v>請求確認</x:v>
       </x:c>
       <x:c r="H21" s="5" t="str"/>
       <x:c r="I21" s="5" t="n">
@@ -3823,11 +3823,11 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="C22" s="12" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D22" s="12" t="str"/>
       <x:c r="E22" s="12" t="str">
-        <x:v>Dahlia Hub subtotal</x:v>
+        <x:v>だりあ東支店 小計</x:v>
       </x:c>
       <x:c r="F22" s="12" t="str"/>
       <x:c r="G22" s="12" t="str"/>
@@ -3872,7 +3872,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AN22" s="12" t="str">
-        <x:v>subtotal row; not an input key</x:v>
+        <x:v>小計行。入力キーではありません。</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -3880,22 +3880,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B23" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C23" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D23" s="5" t="str">
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="E23" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="F23" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="G23" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="H23" s="5" t="str"/>
       <x:c r="I23" s="5" t="n">
@@ -3940,22 +3940,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B24" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C24" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D24" s="5" t="str">
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="E24" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="F24" s="5" t="str">
         <x:v>APP</x:v>
       </x:c>
       <x:c r="G24" s="5" t="str">
-        <x:v>App Support</x:v>
+        <x:v>アプリ支援</x:v>
       </x:c>
       <x:c r="H24" s="5" t="n">
         <x:v>1</x:v>
@@ -4000,22 +4000,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B25" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C25" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D25" s="5" t="str">
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="E25" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="F25" s="5" t="str">
         <x:v>CON</x:v>
       </x:c>
       <x:c r="G25" s="5" t="str">
-        <x:v>Contract Desk</x:v>
+        <x:v>契約確認</x:v>
       </x:c>
       <x:c r="H25" s="5" t="str"/>
       <x:c r="I25" s="5" t="str"/>
@@ -4056,22 +4056,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B26" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C26" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D26" s="5" t="str">
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="E26" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="F26" s="5" t="str">
         <x:v>OTH</x:v>
       </x:c>
       <x:c r="G26" s="5" t="str">
-        <x:v>Other Desk</x:v>
+        <x:v>その他対応</x:v>
       </x:c>
       <x:c r="H26" s="5" t="str"/>
       <x:c r="I26" s="5" t="str"/>
@@ -4112,14 +4112,14 @@
         <x:v>SUBTOTAL</x:v>
       </x:c>
       <x:c r="B27" s="12" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C27" s="12" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D27" s="12" t="str"/>
       <x:c r="E27" s="12" t="str">
-        <x:v>South small-branch subtotal</x:v>
+        <x:v>南部小支店 小計</x:v>
       </x:c>
       <x:c r="F27" s="12" t="str"/>
       <x:c r="G27" s="12" t="str"/>
@@ -4164,7 +4164,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AN27" s="12" t="str">
-        <x:v>subtotal row; not an input key</x:v>
+        <x:v>小計行。入力キーではありません。</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -4172,22 +4172,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B28" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C28" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D28" s="5" t="str">
         <x:v>BR06</x:v>
       </x:c>
       <x:c r="E28" s="5" t="str">
-        <x:v>Fennel South</x:v>
+        <x:v>ふじ南支店</x:v>
       </x:c>
       <x:c r="F28" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="G28" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="H28" s="5" t="str"/>
       <x:c r="I28" s="5" t="str"/>
@@ -4232,22 +4232,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B29" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C29" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D29" s="5" t="str">
         <x:v>BR06</x:v>
       </x:c>
       <x:c r="E29" s="5" t="str">
-        <x:v>Fennel South</x:v>
+        <x:v>ふじ南支店</x:v>
       </x:c>
       <x:c r="F29" s="5" t="str">
         <x:v>DEL</x:v>
       </x:c>
       <x:c r="G29" s="5" t="str">
-        <x:v>Delivery Desk</x:v>
+        <x:v>配送調整</x:v>
       </x:c>
       <x:c r="H29" s="5" t="str"/>
       <x:c r="I29" s="5" t="str"/>
@@ -4288,22 +4288,22 @@
         <x:v>DETAIL</x:v>
       </x:c>
       <x:c r="B30" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
       <x:c r="C30" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D30" s="5" t="str">
         <x:v>BR06</x:v>
       </x:c>
       <x:c r="E30" s="5" t="str">
-        <x:v>Fennel South</x:v>
+        <x:v>ふじ南支店</x:v>
       </x:c>
       <x:c r="F30" s="5" t="str">
         <x:v>OTH</x:v>
       </x:c>
       <x:c r="G30" s="5" t="str">
-        <x:v>Other Desk</x:v>
+        <x:v>その他対応</x:v>
       </x:c>
       <x:c r="H30" s="5" t="n">
         <x:v>2</x:v>
@@ -4352,33 +4352,33 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="31.5" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="13.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12.5" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="13.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="12.75" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14.25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12.25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="8.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.380000114440918" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
-        <x:v>Branch master</x:v>
+        <x:v>支店マスタ</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="10" t="str">
-        <x:v>branch_code</x:v>
+        <x:v>支店コード</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>branch_name</x:v>
+        <x:v>支店名</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
-        <x:v>region</x:v>
+        <x:v>地域</x:v>
       </x:c>
       <x:c r="D2" s="10" t="str">
-        <x:v>branch_size</x:v>
+        <x:v>支店区分</x:v>
       </x:c>
       <x:c r="E2" s="10" t="str">
-        <x:v>subtotal_group</x:v>
+        <x:v>小計グループ</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -4386,13 +4386,13 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="C3" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
-        <x:v>large</x:v>
+        <x:v>大支店</x:v>
       </x:c>
       <x:c r="E3" s="5" t="str">
         <x:v>BR01</x:v>
@@ -4403,16 +4403,16 @@
         <x:v>BR02</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
-        <x:v>Beryl Annex</x:v>
+        <x:v>ひすい北支店</x:v>
       </x:c>
       <x:c r="C4" s="5" t="str">
-        <x:v>North</x:v>
+        <x:v>北部</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
-        <x:v>small</x:v>
+        <x:v>小支店</x:v>
       </x:c>
       <x:c r="E4" s="5" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -4420,16 +4420,16 @@
         <x:v>BR03</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>Cobalt East</x:v>
+        <x:v>こはく東支店</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>small</x:v>
+        <x:v>小支店</x:v>
       </x:c>
       <x:c r="E5" s="5" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -4437,13 +4437,13 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
-        <x:v>East</x:v>
+        <x:v>東部</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
-        <x:v>large</x:v>
+        <x:v>大支店</x:v>
       </x:c>
       <x:c r="E6" s="5" t="str">
         <x:v>BR04</x:v>
@@ -4454,16 +4454,16 @@
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
-        <x:v>small</x:v>
+        <x:v>小支店</x:v>
       </x:c>
       <x:c r="E7" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -4471,29 +4471,29 @@
         <x:v>BR06</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
-        <x:v>Fennel South</x:v>
+        <x:v>ふじ南支店</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
-        <x:v>South</x:v>
+        <x:v>南部</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
-        <x:v>small</x:v>
+        <x:v>小支店</x:v>
       </x:c>
       <x:c r="E8" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
-        <x:v>Business line master</x:v>
+        <x:v>業務マスタ</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="10" t="str">
-        <x:v>business_code</x:v>
+        <x:v>業務コード</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>business_name</x:v>
+        <x:v>業務名</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -4501,7 +4501,7 @@
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="B13" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -4509,7 +4509,7 @@
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="B14" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -4517,7 +4517,7 @@
         <x:v>REP</x:v>
       </x:c>
       <x:c r="B15" s="5" t="str">
-        <x:v>Repair Desk</x:v>
+        <x:v>修理受付</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -4525,7 +4525,7 @@
         <x:v>DEL</x:v>
       </x:c>
       <x:c r="B16" s="5" t="str">
-        <x:v>Delivery Desk</x:v>
+        <x:v>配送調整</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -4533,7 +4533,7 @@
         <x:v>BIL</x:v>
       </x:c>
       <x:c r="B17" s="5" t="str">
-        <x:v>Billing Desk</x:v>
+        <x:v>請求確認</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -4541,7 +4541,7 @@
         <x:v>APP</x:v>
       </x:c>
       <x:c r="B18" s="5" t="str">
-        <x:v>App Support</x:v>
+        <x:v>アプリ支援</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -4549,7 +4549,7 @@
         <x:v>CON</x:v>
       </x:c>
       <x:c r="B19" s="5" t="str">
-        <x:v>Contract Desk</x:v>
+        <x:v>契約確認</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -4557,29 +4557,29 @@
         <x:v>OTH</x:v>
       </x:c>
       <x:c r="B20" s="5" t="str">
-        <x:v>Other Desk</x:v>
+        <x:v>その他対応</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
-        <x:v>Supported branch/business combinations</x:v>
+        <x:v>支店・業務対応表</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="10" t="str">
-        <x:v>branch_code</x:v>
+        <x:v>支店コード</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>branch_name</x:v>
+        <x:v>支店名</x:v>
       </x:c>
       <x:c r="C24" s="10" t="str">
-        <x:v>business_code</x:v>
+        <x:v>業務コード</x:v>
       </x:c>
       <x:c r="D24" s="10" t="str">
-        <x:v>business_name</x:v>
+        <x:v>業務名</x:v>
       </x:c>
       <x:c r="E24" s="10" t="str">
-        <x:v>subtotal_group</x:v>
+        <x:v>小計グループ</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -4587,13 +4587,13 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="B25" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="C25" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="D25" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="E25" s="5" t="str">
         <x:v>BR01</x:v>
@@ -4604,13 +4604,13 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="B26" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="C26" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="D26" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="E26" s="5" t="str">
         <x:v>BR01</x:v>
@@ -4621,13 +4621,13 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="B27" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="C27" s="5" t="str">
         <x:v>REP</x:v>
       </x:c>
       <x:c r="D27" s="5" t="str">
-        <x:v>Repair Desk</x:v>
+        <x:v>修理受付</x:v>
       </x:c>
       <x:c r="E27" s="5" t="str">
         <x:v>BR01</x:v>
@@ -4638,13 +4638,13 @@
         <x:v>BR01</x:v>
       </x:c>
       <x:c r="B28" s="5" t="str">
-        <x:v>Aster Central</x:v>
+        <x:v>あかね中央支店</x:v>
       </x:c>
       <x:c r="C28" s="5" t="str">
         <x:v>BIL</x:v>
       </x:c>
       <x:c r="D28" s="5" t="str">
-        <x:v>Billing Desk</x:v>
+        <x:v>請求確認</x:v>
       </x:c>
       <x:c r="E28" s="5" t="str">
         <x:v>BR01</x:v>
@@ -4655,16 +4655,16 @@
         <x:v>BR02</x:v>
       </x:c>
       <x:c r="B29" s="5" t="str">
-        <x:v>Beryl Annex</x:v>
+        <x:v>ひすい北支店</x:v>
       </x:c>
       <x:c r="C29" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="D29" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="E29" s="5" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -4672,16 +4672,16 @@
         <x:v>BR02</x:v>
       </x:c>
       <x:c r="B30" s="5" t="str">
-        <x:v>Beryl Annex</x:v>
+        <x:v>ひすい北支店</x:v>
       </x:c>
       <x:c r="C30" s="5" t="str">
         <x:v>DEL</x:v>
       </x:c>
       <x:c r="D30" s="5" t="str">
-        <x:v>Delivery Desk</x:v>
+        <x:v>配送調整</x:v>
       </x:c>
       <x:c r="E30" s="5" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -4689,16 +4689,16 @@
         <x:v>BR02</x:v>
       </x:c>
       <x:c r="B31" s="5" t="str">
-        <x:v>Beryl Annex</x:v>
+        <x:v>ひすい北支店</x:v>
       </x:c>
       <x:c r="C31" s="5" t="str">
         <x:v>APP</x:v>
       </x:c>
       <x:c r="D31" s="5" t="str">
-        <x:v>App Support</x:v>
+        <x:v>アプリ支援</x:v>
       </x:c>
       <x:c r="E31" s="5" t="str">
-        <x:v>North Small</x:v>
+        <x:v>北部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -4706,16 +4706,16 @@
         <x:v>BR03</x:v>
       </x:c>
       <x:c r="B32" s="5" t="str">
-        <x:v>Cobalt East</x:v>
+        <x:v>こはく東支店</x:v>
       </x:c>
       <x:c r="C32" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="D32" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="E32" s="5" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -4723,16 +4723,16 @@
         <x:v>BR03</x:v>
       </x:c>
       <x:c r="B33" s="5" t="str">
-        <x:v>Cobalt East</x:v>
+        <x:v>こはく東支店</x:v>
       </x:c>
       <x:c r="C33" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="D33" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="E33" s="5" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -4740,16 +4740,16 @@
         <x:v>BR03</x:v>
       </x:c>
       <x:c r="B34" s="5" t="str">
-        <x:v>Cobalt East</x:v>
+        <x:v>こはく東支店</x:v>
       </x:c>
       <x:c r="C34" s="5" t="str">
         <x:v>CON</x:v>
       </x:c>
       <x:c r="D34" s="5" t="str">
-        <x:v>Contract Desk</x:v>
+        <x:v>契約確認</x:v>
       </x:c>
       <x:c r="E34" s="5" t="str">
-        <x:v>East Small</x:v>
+        <x:v>東部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -4757,13 +4757,13 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="B35" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="C35" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="D35" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="E35" s="5" t="str">
         <x:v>BR04</x:v>
@@ -4774,13 +4774,13 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="B36" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="C36" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="D36" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="E36" s="5" t="str">
         <x:v>BR04</x:v>
@@ -4791,13 +4791,13 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="B37" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="C37" s="5" t="str">
         <x:v>REP</x:v>
       </x:c>
       <x:c r="D37" s="5" t="str">
-        <x:v>Repair Desk</x:v>
+        <x:v>修理受付</x:v>
       </x:c>
       <x:c r="E37" s="5" t="str">
         <x:v>BR04</x:v>
@@ -4808,13 +4808,13 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="B38" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="C38" s="5" t="str">
         <x:v>DEL</x:v>
       </x:c>
       <x:c r="D38" s="5" t="str">
-        <x:v>Delivery Desk</x:v>
+        <x:v>配送調整</x:v>
       </x:c>
       <x:c r="E38" s="5" t="str">
         <x:v>BR04</x:v>
@@ -4825,13 +4825,13 @@
         <x:v>BR04</x:v>
       </x:c>
       <x:c r="B39" s="5" t="str">
-        <x:v>Dahlia Hub</x:v>
+        <x:v>だりあ東支店</x:v>
       </x:c>
       <x:c r="C39" s="5" t="str">
         <x:v>BIL</x:v>
       </x:c>
       <x:c r="D39" s="5" t="str">
-        <x:v>Billing Desk</x:v>
+        <x:v>請求確認</x:v>
       </x:c>
       <x:c r="E39" s="5" t="str">
         <x:v>BR04</x:v>
@@ -4842,16 +4842,16 @@
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="B40" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="C40" s="5" t="str">
         <x:v>INQ</x:v>
       </x:c>
       <x:c r="D40" s="5" t="str">
-        <x:v>Inquiry Desk</x:v>
+        <x:v>問合せ受付</x:v>
       </x:c>
       <x:c r="E40" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -4859,16 +4859,16 @@
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="B41" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="C41" s="5" t="str">
         <x:v>APP</x:v>
       </x:c>
       <x:c r="D41" s="5" t="str">
-        <x:v>App Support</x:v>
+        <x:v>アプリ支援</x:v>
       </x:c>
       <x:c r="E41" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -4876,16 +4876,16 @@
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="B42" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="C42" s="5" t="str">
         <x:v>CON</x:v>
       </x:c>
       <x:c r="D42" s="5" t="str">
-        <x:v>Contract Desk</x:v>
+        <x:v>契約確認</x:v>
       </x:c>
       <x:c r="E42" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -4893,16 +4893,16 @@
         <x:v>BR05</x:v>
       </x:c>
       <x:c r="B43" s="5" t="str">
-        <x:v>Elm South</x:v>
+        <x:v>えのき南支店</x:v>
       </x:c>
       <x:c r="C43" s="5" t="str">
         <x:v>OTH</x:v>
       </x:c>
       <x:c r="D43" s="5" t="str">
-        <x:v>Other Desk</x:v>
+        <x:v>その他対応</x:v>
       </x:c>
       <x:c r="E43" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -4910,16 +4910,16 @@
         <x:v>BR06</x:v>
       </x:c>
       <x:c r="B44" s="5" t="str">
-        <x:v>Fennel South</x:v>
+        <x:v>ふじ南支店</x:v>
       </x:c>
       <x:c r="C44" s="5" t="str">
         <x:v>RSP</x:v>
       </x:c>
       <x:c r="D44" s="5" t="str">
-        <x:v>Response Desk</x:v>
+        <x:v>初動対応</x:v>
       </x:c>
       <x:c r="E44" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -4927,16 +4927,16 @@
         <x:v>BR06</x:v>
       </x:c>
       <x:c r="B45" s="5" t="str">
-        <x:v>Fennel South</x:v>
+        <x:v>ふじ南支店</x:v>
       </x:c>
       <x:c r="C45" s="5" t="str">
         <x:v>DEL</x:v>
       </x:c>
       <x:c r="D45" s="5" t="str">
-        <x:v>Delivery Desk</x:v>
+        <x:v>配送調整</x:v>
       </x:c>
       <x:c r="E45" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -4944,16 +4944,16 @@
         <x:v>BR06</x:v>
       </x:c>
       <x:c r="B46" s="5" t="str">
-        <x:v>Fennel South</x:v>
+        <x:v>ふじ南支店</x:v>
       </x:c>
       <x:c r="C46" s="5" t="str">
         <x:v>OTH</x:v>
       </x:c>
       <x:c r="D46" s="5" t="str">
-        <x:v>Other Desk</x:v>
+        <x:v>その他対応</x:v>
       </x:c>
       <x:c r="E46" s="5" t="str">
-        <x:v>South Small</x:v>
+        <x:v>南部小支店</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4968,33 +4968,33 @@
     <x:col min="1" max="1" width="6.880000114440918" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="9.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="19.3799991607666" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="9.25" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="6.5" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="5.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="21.1299991607666" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="27" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="10" t="str">
-        <x:v>month</x:v>
+        <x:v>対象月</x:v>
       </x:c>
       <x:c r="B1" s="10" t="str">
-        <x:v>date</x:v>
+        <x:v>日付</x:v>
       </x:c>
       <x:c r="C1" s="10" t="str">
-        <x:v>file_name</x:v>
+        <x:v>ファイル名</x:v>
       </x:c>
       <x:c r="D1" s="10" t="str">
-        <x:v>subfolder</x:v>
+        <x:v>サブフォルダ</x:v>
       </x:c>
       <x:c r="E1" s="10" t="str">
-        <x:v>row_no</x:v>
+        <x:v>行番号</x:v>
       </x:c>
       <x:c r="F1" s="10" t="str">
-        <x:v>issue_type</x:v>
+        <x:v>異常種別</x:v>
       </x:c>
       <x:c r="G1" s="10" t="str">
-        <x:v>expected_behavior</x:v>
+        <x:v>期待動作</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -5017,7 +5017,7 @@
         <x:v>unknown_branch</x:v>
       </x:c>
       <x:c r="G2" s="5" t="str">
-        <x:v>skip and log unknown branch</x:v>
+        <x:v>未知の支店として転記せずログ記録</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -5040,7 +5040,7 @@
         <x:v>non_numeric_count</x:v>
       </x:c>
       <x:c r="G3" s="5" t="str">
-        <x:v>skip and log non numeric count</x:v>
+        <x:v>非数値件数として転記せずログ記録</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -5063,7 +5063,7 @@
         <x:v>blank_count</x:v>
       </x:c>
       <x:c r="G4" s="5" t="str">
-        <x:v>skip and log blank count</x:v>
+        <x:v>空欄件数として転記せずログ記録</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -5082,7 +5082,7 @@
         <x:v>missing_day</x:v>
       </x:c>
       <x:c r="G5" s="5" t="str">
-        <x:v>no transfer; day column remains blank</x:v>
+        <x:v>転記なし。日付列は空欄のまま</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -5097,7 +5097,7 @@
         <x:v>out_of_month_day_column</x:v>
       </x:c>
       <x:c r="G6" s="5" t="str">
-        <x:v>day 29 remains blank for 2026-02</x:v>
+        <x:v>2026-02 の 29 日列は空欄のまま</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -5112,7 +5112,7 @@
         <x:v>out_of_month_day_column</x:v>
       </x:c>
       <x:c r="G7" s="5" t="str">
-        <x:v>day 30 remains blank for 2026-02</x:v>
+        <x:v>2026-02 の 30 日列は空欄のまま</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -5127,7 +5127,7 @@
         <x:v>out_of_month_day_column</x:v>
       </x:c>
       <x:c r="G8" s="5" t="str">
-        <x:v>day 31 remains blank for 2026-02</x:v>
+        <x:v>2026-02 の 31 日列は空欄のまま</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
